--- a/tools/importer/reports/import-product-category-page.report.xlsx
+++ b/tools/importer/reports/import-product-category-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,48 @@
     <t>url</t>
   </si>
   <si>
+    <t>en-us/lp/disaggregated-infrastructure.report.json</t>
+  </si>
+  <si>
+    <t>["hero","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/disaggregated-infrastructure</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>solutions-landing-page</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:51:09.639Z</t>
+  </si>
+  <si>
+    <t>Disaggregated Infrastructure | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/disaggregated-infrastructure</t>
+  </si>
+  <si>
+    <t>en-us/lp/enterprise-upgrades.report.json</t>
+  </si>
+  <si>
+    <t>["cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/enterprise-upgrades</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:51:24.517Z</t>
+  </si>
+  <si>
+    <t>Dell Technologies - Enterprise Upgrades For Your Server | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/enterprise-upgrades</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/customer-stories-mclaren-racing.report.json</t>
   </si>
   <si>
@@ -46,9 +88,6 @@
     <t>en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>customer-story-page</t>
   </si>
   <si>
@@ -61,6 +100,24 @@
     <t>https://www.dell.com/en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
+    <t>en-us/lp/dt/energy-efficient-data-center.report.json</t>
+  </si>
+  <si>
+    <t>["cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/energy-efficient-data-center</t>
+  </si>
+  <si>
+    <t>2026-03-16T12:51:15.802Z</t>
+  </si>
+  <si>
+    <t>Energy-Efficient Data Center | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/energy-efficient-data-center</t>
+  </si>
+  <si>
     <t>en-us/shop/scc/sc/apex.report.json</t>
   </si>
   <si>
@@ -73,7 +130,7 @@
     <t>product-category-page</t>
   </si>
   <si>
-    <t>2026-03-16T12:50:15.193Z</t>
+    <t>2026-03-16T13:08:41.909Z</t>
   </si>
   <si>
     <t>Dell APEX Subscription &amp; as-a-Service Solutions | Dell USA</t>
@@ -112,7 +169,7 @@
     <t>en-us/shop/scc/sc/cyber-resilience</t>
   </si>
   <si>
-    <t>2026-03-16T12:50:38.523Z</t>
+    <t>2026-03-16T13:09:09.465Z</t>
   </si>
   <si>
     <t>Cyber Resilience – Data Backup Solutions | Dell USA</t>
@@ -130,7 +187,7 @@
     <t>en-us/shop/scc/sc/networking-products</t>
   </si>
   <si>
-    <t>2026-03-16T12:50:53.155Z</t>
+    <t>2026-03-16T13:09:24.980Z</t>
   </si>
   <si>
     <t>Networking Solutions - Scalable, AI-Ready Infrastructure | Dell USA</t>
@@ -148,7 +205,7 @@
     <t>en-us/shop/scc/sc/private-cloud-solutions</t>
   </si>
   <si>
-    <t>2026-03-16T12:50:46.332Z</t>
+    <t>2026-03-16T13:09:18.537Z</t>
   </si>
   <si>
     <t>Private Cloud and HCI Solutions | Dell USA</t>
@@ -166,7 +223,7 @@
     <t>en-us/shop/scc/sc/servers</t>
   </si>
   <si>
-    <t>2026-03-16T12:50:22.349Z</t>
+    <t>2026-03-16T13:08:50.538Z</t>
   </si>
   <si>
     <t>Servers - Rack, Tower &amp; Edge Servers | Dell USA</t>
@@ -184,7 +241,7 @@
     <t>en-us/shop/scc/sc/storage-products</t>
   </si>
   <si>
-    <t>2026-03-16T12:50:30.047Z</t>
+    <t>2026-03-16T13:08:59.006Z</t>
   </si>
   <si>
     <t>Enterprise Data Storage: Cloud, NAS, &amp; Flash Storage | Dell USA</t>
@@ -579,12 +636,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
-    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
@@ -655,85 +712,85 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
         <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
@@ -759,68 +816,146 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-product-category-page.report.xlsx
+++ b/tools/importer/reports/import-product-category-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>solutions-landing-page</t>
   </si>
   <si>
-    <t>2026-03-16T12:51:09.639Z</t>
+    <t>2026-03-16T13:09:36.330Z</t>
   </si>
   <si>
     <t>Disaggregated Infrastructure | Dell USA</t>
@@ -70,7 +70,7 @@
     <t>en-us/lp/enterprise-upgrades</t>
   </si>
   <si>
-    <t>2026-03-16T12:51:24.517Z</t>
+    <t>2026-03-16T13:09:51.248Z</t>
   </si>
   <si>
     <t>Dell Technologies - Enterprise Upgrades For Your Server | Dell USA</t>
@@ -91,7 +91,7 @@
     <t>customer-story-page</t>
   </si>
   <si>
-    <t>2026-03-16T12:29:34.829Z</t>
+    <t>2026-03-16T13:10:23.041Z</t>
   </si>
   <si>
     <t>McLaren Formula 1® Team | Dell USA</t>
@@ -100,6 +100,24 @@
     <t>https://www.dell.com/en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
+    <t>en-us/lp/dt/devops-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["columns","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/devops-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:10:57.139Z</t>
+  </si>
+  <si>
+    <t>Developers &amp; DevOps | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/devops-solutions</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/energy-efficient-data-center.report.json</t>
   </si>
   <si>
@@ -109,7 +127,7 @@
     <t>en-us/lp/dt/energy-efficient-data-center</t>
   </si>
   <si>
-    <t>2026-03-16T12:51:15.802Z</t>
+    <t>2026-03-16T13:09:43.809Z</t>
   </si>
   <si>
     <t>Energy-Efficient Data Center | Dell USA</t>
@@ -118,6 +136,24 @@
     <t>https://www.dell.com/en-us/lp/dt/energy-efficient-data-center</t>
   </si>
   <si>
+    <t>en-us/lp/dt/payment-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["columns","columns","columns","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/payment-solutions</t>
+  </si>
+  <si>
+    <t>2026-03-16T13:10:47.301Z</t>
+  </si>
+  <si>
+    <t>Payment Solutions | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/payment-solutions</t>
+  </si>
+  <si>
     <t>en-us/shop/scc/sc/apex.report.json</t>
   </si>
   <si>
@@ -130,7 +166,7 @@
     <t>product-category-page</t>
   </si>
   <si>
-    <t>2026-03-16T13:08:41.909Z</t>
+    <t>2026-03-16T13:21:39.190Z</t>
   </si>
   <si>
     <t>Dell APEX Subscription &amp; as-a-Service Solutions | Dell USA</t>
@@ -151,7 +187,7 @@
     <t>ai-solutions-page</t>
   </si>
   <si>
-    <t>2026-03-16T12:28:46.522Z</t>
+    <t>2026-03-16T13:10:09.017Z</t>
   </si>
   <si>
     <t>Artificial Intelligence Solutions | Dell USA</t>
@@ -169,7 +205,7 @@
     <t>en-us/shop/scc/sc/cyber-resilience</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:09.465Z</t>
+    <t>2026-03-16T13:22:02.845Z</t>
   </si>
   <si>
     <t>Cyber Resilience – Data Backup Solutions | Dell USA</t>
@@ -187,7 +223,7 @@
     <t>en-us/shop/scc/sc/networking-products</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:24.980Z</t>
+    <t>2026-03-16T13:22:14.986Z</t>
   </si>
   <si>
     <t>Networking Solutions - Scalable, AI-Ready Infrastructure | Dell USA</t>
@@ -205,7 +241,7 @@
     <t>en-us/shop/scc/sc/private-cloud-solutions</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:18.537Z</t>
+    <t>2026-03-16T13:22:08.558Z</t>
   </si>
   <si>
     <t>Private Cloud and HCI Solutions | Dell USA</t>
@@ -223,7 +259,7 @@
     <t>en-us/shop/scc/sc/servers</t>
   </si>
   <si>
-    <t>2026-03-16T13:08:50.538Z</t>
+    <t>2026-03-16T13:21:44.721Z</t>
   </si>
   <si>
     <t>Servers - Rack, Tower &amp; Edge Servers | Dell USA</t>
@@ -241,7 +277,7 @@
     <t>en-us/shop/scc/sc/storage-products</t>
   </si>
   <si>
-    <t>2026-03-16T13:08:59.006Z</t>
+    <t>2026-03-16T13:21:54.440Z</t>
   </si>
   <si>
     <t>Enterprise Data Storage: Cloud, NAS, &amp; Flash Storage | Dell USA</t>
@@ -636,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -790,85 +826,85 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>45</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>46</v>
-      </c>
-      <c r="G7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>52</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>53</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>56</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
         <v>57</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
@@ -894,7 +930,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
         <v>64</v>
@@ -920,7 +956,7 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s">
         <v>70</v>
@@ -946,7 +982,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
         <v>76</v>
@@ -956,6 +992,58 @@
       </c>
       <c r="H12" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-product-category-page.report.xlsx
+++ b/tools/importer/reports/import-product-category-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="170">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>solutions-landing-page</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:36.330Z</t>
+    <t>2026-03-16T13:22:45.162Z</t>
   </si>
   <si>
     <t>Disaggregated Infrastructure | Dell USA</t>
@@ -70,7 +70,7 @@
     <t>en-us/lp/enterprise-upgrades</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:51.248Z</t>
+    <t>2026-03-16T13:23:01.130Z</t>
   </si>
   <si>
     <t>Dell Technologies - Enterprise Upgrades For Your Server | Dell USA</t>
@@ -79,6 +79,27 @@
     <t>https://www.dell.com/en-us/lp/enterprise-upgrades</t>
   </si>
   <si>
+    <t>en-us/lp/dt/artificial-intelligence-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns","columns","cards","cards","cards","carousel","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/artificial-intelligence-services</t>
+  </si>
+  <si>
+    <t>services-detail-page</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:06:31.146Z</t>
+  </si>
+  <si>
+    <t>AI Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/artificial-intelligence-services</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/customer-stories-mclaren-racing.report.json</t>
   </si>
   <si>
@@ -91,7 +112,7 @@
     <t>customer-story-page</t>
   </si>
   <si>
-    <t>2026-03-16T13:10:23.041Z</t>
+    <t>2026-03-16T13:23:29.485Z</t>
   </si>
   <si>
     <t>McLaren Formula 1® Team | Dell USA</t>
@@ -100,6 +121,24 @@
     <t>https://www.dell.com/en-us/lp/dt/customer-stories-mclaren-racing</t>
   </si>
   <si>
+    <t>en-us/lp/dt/deployment-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","columns","columns","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/deployment-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:07:01.557Z</t>
+  </si>
+  <si>
+    <t>Deployment Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/deployment-services</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/devops-solutions.report.json</t>
   </si>
   <si>
@@ -109,7 +148,7 @@
     <t>en-us/lp/dt/devops-solutions</t>
   </si>
   <si>
-    <t>2026-03-16T13:10:57.139Z</t>
+    <t>2026-03-16T13:22:37.890Z</t>
   </si>
   <si>
     <t>Developers &amp; DevOps | Dell USA</t>
@@ -127,7 +166,7 @@
     <t>en-us/lp/dt/energy-efficient-data-center</t>
   </si>
   <si>
-    <t>2026-03-16T13:09:43.809Z</t>
+    <t>2026-03-16T13:22:52.770Z</t>
   </si>
   <si>
     <t>Energy-Efficient Data Center | Dell USA</t>
@@ -136,6 +175,78 @@
     <t>https://www.dell.com/en-us/lp/dt/energy-efficient-data-center</t>
   </si>
   <si>
+    <t>en-us/lp/dt/lifecycle-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/lifecycle-services</t>
+  </si>
+  <si>
+    <t>services-category-page</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:04:40.878Z</t>
+  </si>
+  <si>
+    <t>Lifecycle Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/lifecycle-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/managed-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","columns","columns","columns","cards","cards","cards","cards","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/managed-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:07:06.968Z</t>
+  </si>
+  <si>
+    <t>Managed Services and Residency Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/managed-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/modern-workforce.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","cards","cards","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/modern-workforce</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:06:46.754Z</t>
+  </si>
+  <si>
+    <t>Modern Workforce Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/modern-workforce</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/multicloud-services.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/multicloud-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:06:40.037Z</t>
+  </si>
+  <si>
+    <t>Multicloud Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/multicloud-services</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/payment-solutions.report.json</t>
   </si>
   <si>
@@ -145,7 +256,7 @@
     <t>en-us/lp/dt/payment-solutions</t>
   </si>
   <si>
-    <t>2026-03-16T13:10:47.301Z</t>
+    <t>2026-03-16T13:22:31.578Z</t>
   </si>
   <si>
     <t>Payment Solutions | Dell USA</t>
@@ -154,6 +265,132 @@
     <t>https://www.dell.com/en-us/lp/dt/payment-solutions</t>
   </si>
   <si>
+    <t>en-us/lp/dt/professional-services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","carousel","carousel","columns","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/professional-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:04:34.680Z</t>
+  </si>
+  <si>
+    <t>Professional Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/professional-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/recovery-recycling-services.report.json</t>
+  </si>
+  <si>
+    <t>["cards","cards","cards","carousel","carousel"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/recovery-recycling-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:07:20.907Z</t>
+  </si>
+  <si>
+    <t>Recovery and Recycling Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/recovery-recycling-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/security-and-resiliency.report.json</t>
+  </si>
+  <si>
+    <t>["cards","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/security-and-resiliency</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:06:54.385Z</t>
+  </si>
+  <si>
+    <t>Security and Resilience Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/security-and-resiliency</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/services.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","columns","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/services</t>
+  </si>
+  <si>
+    <t>services-hub-page</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:04:18.810Z</t>
+  </si>
+  <si>
+    <t>View All Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/support-services.report.json</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/support-services</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:07:14.547Z</t>
+  </si>
+  <si>
+    <t>Support Services | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/support-services</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/technologies-and-tools.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","columns","columns","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/technologies-and-tools</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:06:26.016Z</t>
+  </si>
+  <si>
+    <t>Technologies and Tools | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/technologies-and-tools</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/training-and-certification.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","cards"]</t>
+  </si>
+  <si>
+    <t>en-us/lp/dt/training-and-certification</t>
+  </si>
+  <si>
+    <t>2026-03-16T17:06:20.627Z</t>
+  </si>
+  <si>
+    <t>Training and Certification | Dell USA</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/en-us/lp/dt/training-and-certification</t>
+  </si>
+  <si>
     <t>en-us/shop/scc/sc/apex.report.json</t>
   </si>
   <si>
@@ -187,7 +424,7 @@
     <t>ai-solutions-page</t>
   </si>
   <si>
-    <t>2026-03-16T13:10:09.017Z</t>
+    <t>2026-03-16T13:23:21.722Z</t>
   </si>
   <si>
     <t>Artificial Intelligence Solutions | Dell USA</t>
@@ -217,13 +454,13 @@
     <t>en-us/shop/scc/sc/networking-products.report.json</t>
   </si>
   <si>
-    <t>["hero","cards","cards","accordion","accordion","tabs"]</t>
+    <t>["hero","cards","cards","value-pillars","accordion","accordion","tabs"]</t>
   </si>
   <si>
     <t>en-us/shop/scc/sc/networking-products</t>
   </si>
   <si>
-    <t>2026-03-16T13:22:14.986Z</t>
+    <t>2026-03-16T20:19:05.600Z</t>
   </si>
   <si>
     <t>Networking Solutions - Scalable, AI-Ready Infrastructure | Dell USA</t>
@@ -672,11 +909,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="8" width="50" customWidth="1"/>
@@ -800,53 +1037,53 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -855,30 +1092,30 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>
@@ -930,7 +1167,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
         <v>64</v>
@@ -956,7 +1193,7 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
         <v>70</v>
@@ -973,77 +1210,415 @@
         <v>73</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
         <v>74</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
         <v>75</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>76</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>77</v>
-      </c>
-      <c r="H12" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
         <v>79</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>80</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
         <v>81</v>
       </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>82</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>83</v>
-      </c>
-      <c r="H13" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
         <v>85</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>86</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" t="s">
         <v>87</v>
       </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>88</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>89</v>
       </c>
-      <c r="H14" t="s">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" t="s">
+        <v>131</v>
+      </c>
+      <c r="H21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" t="s">
+        <v>137</v>
+      </c>
+      <c r="G22" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" t="s">
+        <v>143</v>
+      </c>
+      <c r="G23" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" t="s">
+        <v>149</v>
+      </c>
+      <c r="G24" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" t="s">
+        <v>155</v>
+      </c>
+      <c r="G25" t="s">
+        <v>156</v>
+      </c>
+      <c r="H25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G26" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" t="s">
+        <v>167</v>
+      </c>
+      <c r="G27" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
